--- a/output/2026-08-31_09_Italia_Toscana_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-08-31_09_Italia_Toscana_Depolverazione_Trattamento_aria.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Impianti di aspirazione industriale, filtrazione aria, depolverazione; attiva dal 1979.</t>
+          <t>Impianti di aspirazione industriale, filtrazione aria, depolverazione; attiva dal 1979. [DUPLICATO — vedi anche: 2026-08-31_08_Italia_Toscana_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Impianti di aspirazione industriale e canalizzazioni.</t>
+          <t>Impianti di aspirazione industriale e canalizzazioni. [DUPLICATO — vedi anche: 2026-08-31_08_Italia_Toscana_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Azienda dal 1990 (esperienza dal 1970), impianti di aspirazione/depolverazione/filtrazione fumi e polveri. NOTA: le voci grezze 'Toscana Impianti Srl' (Pisa) e 'Toscana Impianti Srl' (Grosseto) risultano riferirsi allo stesso sito/contatti di questa azienda: deduplicate qui.</t>
+          <t>Azienda dal 1990 (esperienza dal 1970), impianti di aspirazione/depolverazione/filtrazione fumi e polveri. NOTA: le voci grezze 'Toscana Impianti Srl' (Pisa) e 'Toscana Impianti Srl' (Grosseto) risultano riferirsi allo stesso sito/contatti di questa azienda: deduplicate qui. [DUPLICATO — vedi anche: 2026-08-31_08_Italia_Toscana_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Aspirazione industriale, trattamento fumi di saldatura, filtri a maniche/cartucce/carboni attivi.</t>
+          <t>Aspirazione industriale, trattamento fumi di saldatura, filtri a maniche/cartucce/carboni attivi. [DUPLICATO — vedi anche: 2026-08-31_08_Italia_Toscana_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Vendita/noleggio aspiratori industriali (liquidi/polveri); attiva dal 1980.</t>
+          <t>Vendita/noleggio aspiratori industriali (liquidi/polveri); attiva dal 1980. [DUPLICATO — vedi anche: 2026-08-31_08_Italia_Toscana_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Distributore aspiratori industriali Coynco. IMPORTANTE: fonti web indicano che distribuisce anche prodotti a marchio DU-PUY - possibile rivenditore gia' attivo del brand, verificare con priorita'.</t>
+          <t>Distributore aspiratori industriali Coynco. IMPORTANTE: fonti web indicano che distribuisce anche prodotti a marchio DU-PUY - possibile rivenditore gia' attivo del brand, verificare con priorita'. [DUPLICATO — vedi anche: 2026-08-31_08_Italia_Toscana_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">

--- a/output/2026-08-31_09_Italia_Toscana_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-08-31_09_Italia_Toscana_Depolverazione_Trattamento_aria.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (31/08/2026)</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (31/08/2026)</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (31/08/2026)</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (31/08/2026)</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (31/08/2026)</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (31/08/2026)</t>
         </is>
       </c>
     </row>
